--- a/downloads/exportExcelCustomerInC_ServiceNormal.xlsx
+++ b/downloads/exportExcelCustomerInC_ServiceNormal.xlsx
@@ -43,7 +43,7 @@
     <t>9123456790</t>
   </si>
   <si>
-    <t>Anil Dubey</t>
+    <t>Anil Rathor</t>
   </si>
   <si>
     <t>akbk6551+1136@gmail.com</t>
